--- a/Custom PCB esp32c6/fab-xiao/jlc/BOM_xiao_jlc.xlsx
+++ b/Custom PCB esp32c6/fab-xiao/jlc/BOM_xiao_jlc.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C398931</t>
+          <t>C86816</t>
         </is>
       </c>
     </row>

--- a/Custom PCB esp32c6/fab-xiao/jlc/BOM_xiao_jlc.xlsx
+++ b/Custom PCB esp32c6/fab-xiao/jlc/BOM_xiao_jlc.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C86816</t>
+          <t>C45783</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C84706</t>
+          <t>C1567</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C5137770</t>
+          <t>C7420372</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C123802</t>
+          <t>C19077509</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C96233</t>
+          <t>C7502707</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C138008</t>
+          <t>C25776</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C1226</t>
+          <t>C22962</t>
         </is>
       </c>
     </row>
